--- a/data/trans_orig/IP42B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13939</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31653</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>40137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44782</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52484</t>
+          <t>51917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58015</t>
+          <t>57998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94749</t>
+          <t>95384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102086</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9853</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20364</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>34536</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43294</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51617</t>
+          <t>51877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>45825</t>
+          <t>46476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92670</t>
+          <t>92678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102216</t>
+          <t>102390</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153873</t>
+          <t>153950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>263721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32280</t>
+          <t>32395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>30156</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65233</t>
+          <t>65274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>76863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>40927</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49582</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48901</t>
+          <t>49510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>58468</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92753</t>
+          <t>93115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106256</t>
+          <t>106835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15744</t>
+          <t>15586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28196</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34477</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>38273</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61535</t>
+          <t>61693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71452</t>
+          <t>71443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30631</t>
+          <t>30404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33542</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66619</t>
+          <t>67082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77151</t>
+          <t>77397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142012</t>
+          <t>141196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168958</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>322955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35417</t>
+          <t>35193</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39304</t>
+          <t>39305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29911</t>
+          <t>29515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67439</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75309</t>
+          <t>75025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>13255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52964</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59906</t>
+          <t>59939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70818</t>
+          <t>70396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76790</t>
+          <t>76817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126811</t>
+          <t>126710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135984</t>
+          <t>135677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40883</t>
+          <t>41147</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47234</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50372</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>56194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93859</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102527</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>49404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93059</t>
+          <t>91885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103645</t>
+          <t>103725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177500</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209718</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222549</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391530</t>
+          <t>391150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410264</t>
+          <t>410378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP42B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,102 +727,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3219</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>19,87%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4697</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18667</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15751</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19368</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>81,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16493</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13939</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13748</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>17158</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>80,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18667</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15861</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19368</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>81,89%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19368</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19368</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19368</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17158</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>17158</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>17158</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19368</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19368</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19368</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6226</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1939</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5262</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5196</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6775</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55971</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>43460</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40137</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44780</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40203</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>44787</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>55971</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>51917</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>57998</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>94834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102133</t>
+          <t>102006</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58692</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>45399</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>45399</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>45399</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>58692</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>58692</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>58692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5670</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2794</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9997</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2983</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6405</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5670</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10168</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24547</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20220</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27423</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>66,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15294</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11782</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17430</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11872</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17481</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24547</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20049</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27367</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30217</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>30217</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30217</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18277</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>18277</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>18277</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>30217</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>30217</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>30217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2672</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6759</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6909</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10863</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3360</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11709</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2672</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49846</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45759</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51804</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>87,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>48293</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>44339</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51877</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>43493</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>51842</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49846</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>46476</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>51858</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92678</t>
+          <t>92438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>101834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52518</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>52518</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>52518</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>55202</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>55202</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>55202</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>52518</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>52518</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>52518</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17578</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7944</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18963</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>149031</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143217</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153769</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123541</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>117674</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128093</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>117074</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128528</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143399</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153950</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263721</t>
+          <t>264867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279503</t>
+          <t>279535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11108</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6632</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11325</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11180</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11322</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34791</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30370</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38237</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>37088</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32395</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>40388</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32540</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>40517</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,83%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>34791</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>30156</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38241</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65274</t>
+          <t>65512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41478</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>41478</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>41478</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43720</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>43720</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>43720</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>41478</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>41478</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>41478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9804</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5678</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14846</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9983</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5785</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14811</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5811</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15033</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9804</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5872</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14830</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>27937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54536</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49494</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58662</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>45755</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40927</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49953</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>40705</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>49927</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54536</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49510</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>58468</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93115</t>
+          <t>92141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106835</t>
+          <t>106884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>64340</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>64340</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>64340</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55738</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>55738</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>55738</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>64340</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>64340</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>64340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5939</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10728</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4003</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1839</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7983</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1382</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8074</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10194</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35024</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30235</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37801</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,28%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32313</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28333</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34477</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28242</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>34934</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35024</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30769</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38273</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71443</t>
+          <t>71032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40963</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40963</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40963</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36316</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36316</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36316</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40963</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>40963</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1808</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8030</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7607</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3926</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12529</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4024</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12516</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7755</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>17560</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37289</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33223</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39445</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35326</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30404</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>39007</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>30417</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38909</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>82,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>70,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37289</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33498</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39649</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,39%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67082</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77397</t>
+          <t>77035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -3929,52 +3929,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>41253</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>41253</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>41253</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>42933</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>42933</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>42933</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>41253</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>41253</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>41253</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18970</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35036</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21221</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37511</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20630</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36151</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19449</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35299</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66645</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>161640</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>152998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>169064</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>150483</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>141196</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>157486</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>142556</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>158077</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>161640</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>152735</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>168585</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300096</t>
+          <t>301228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322955</t>
+          <t>322805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9137</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1643</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4362</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4860</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2201</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9184</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11650</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29562</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36735</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,39%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>38123</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35193</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39305</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35404</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39296</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>95,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,5%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33839</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29515</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36498</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66814</t>
+          <t>66555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38699</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38699</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38699</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>39766</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>39766</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>39766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38699</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38699</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7460</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4570</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9049</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7682</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74810</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>70618</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76796</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57317</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52762</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59939</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>52838</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>59955</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74810</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>70396</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76817</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126710</t>
+          <t>126899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135677</t>
+          <t>136028</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>78078</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>78078</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>78078</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>61887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>61887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>61887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>78078</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>78078</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>78078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7617</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3831</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7844</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7848</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>54043</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49976</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56228</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,63%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>45160</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41147</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47695</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41053</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>47604</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,18%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>54043</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>49745</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>56194</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93882</t>
+          <t>94248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102623</t>
+          <t>102786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57593</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57593</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57593</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>48991</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>48991</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>48991</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>57593</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>57593</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>57593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10412</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6985</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11985</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3782</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12363</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2782</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10761</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54276</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57315</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44445</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39445</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>47907</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39067</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>47648</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>54276</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49404</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>57383</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91885</t>
+          <t>91540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103725</t>
+          <t>103707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>60165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>60165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>60165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>51430</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>51430</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>51430</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>60165</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>60165</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>60165</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11284</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17029</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12180</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24540</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11510</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25294</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>216968</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>209570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>223251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>185044</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>177533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>189893</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>177786</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>190573</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>216968</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>209241</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>223025</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391150</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410378</t>
+          <t>410592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
